--- a/src/Lighting_Designer/02_RIG팩/LXSEQ_RIG_01_ShowBase_r3.xlsx
+++ b/src/Lighting_Designer/02_RIG팩/LXSEQ_RIG_01_ShowBase_r3.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RIG-HEAD" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FIXTURE" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PATCH" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GROUP" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PRESET-DIM·COL" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PRESET-POS·BM" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FX" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONSOLE" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NOTE" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="RIG-HEAD" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FIXTURE" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="PATCH" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="GROUP" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="PRESET-DIM·COL" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="PRESET-POS·BM" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="FX" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="CONSOLE" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="NOTE" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>sACN · Universe 1–4 · Priority 100 · 백업 노드 확인필요</t>
+          <t>sACN · Universe 1–5 (+U6 예비) · Priority 100 · 백업 노드 확인필요</t>
         </is>
       </c>
     </row>
